--- a/series_data/night-shift/series_log.xlsx
+++ b/series_data/night-shift/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -759,6 +759,281 @@
       <c r="M6" t="inlineStr">
         <is>
           <t>C:\Users\ihsan\Desktop\Antigravity\Projects\Youtube\output\series\night-shift\episodes\ep01\shots\shot_05.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-07-04 15:40</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>720p</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>264.0</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/r/4636d081da63054c73310834a1eca176_1783179578_xqnwk7x2.mp4</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/night-shift/episodes/ep02/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-07-04 15:44</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>720p</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>264.0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/seedance/1783179848638-nt7iwj9f15o.mp4</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/night-shift/episodes/ep02/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-07-04 15:48</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>720p</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>330.0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/r/4fc2696da5545f1495314ee99550c103_1783180073_ydpafnpd.mp4</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/night-shift/episodes/ep02/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-07-04 15:52</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>720p</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>330.0</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/r/1e10c6b6e98cebad2528dbda184f1bcf_1783180309_cf2ltf93.mp4</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/night-shift/episodes/ep02/shots/shot_04.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-07-04 15:56</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>720p</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>264.0</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/seedance/1783180543178-fod5i25yt6.mp4</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/night-shift/episodes/ep02/shots/shot_05.mp4</t>
         </is>
       </c>
     </row>
